--- a/STA380GroupForm.xlsx
+++ b/STA380GroupForm.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christianjasonsumitro/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevin/Documents/STA380/STA380-Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7DB9AF7-C497-804E-A3A3-35AF10ED0C1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95322017-E2A4-D041-9D04-2DA988A71EC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="29400" windowHeight="16980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
   <si>
     <t>If left blank, you will be assigned a number.</t>
   </si>
@@ -113,6 +113,9 @@
   </si>
   <si>
     <t>seye edward</t>
+  </si>
+  <si>
+    <t>Inverse TRANSFORM</t>
   </si>
 </sst>
 </file>
@@ -130,6 +133,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -138,6 +142,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -145,6 +150,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -442,6 +448,9 @@
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="B5" s="5" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="3" t="s">

--- a/STA380GroupForm.xlsx
+++ b/STA380GroupForm.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevin/Documents/STA380/STA380-Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95322017-E2A4-D041-9D04-2DA988A71EC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C063D28D-FFAF-7740-9E17-5CF54EBC56D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="29400" windowHeight="16980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
   <si>
     <t>If left blank, you will be assigned a number.</t>
   </si>
@@ -115,14 +115,45 @@
     <t>seye edward</t>
   </si>
   <si>
-    <t>Inverse TRANSFORM</t>
+    <t>Inverse-Transform Method</t>
+  </si>
+  <si>
+    <t>Exponential Distribution</t>
+  </si>
+  <si>
+    <r>
+      <t>1. Comparison Graph:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t> Overlay a histogram of the simulated data with the theoretical Probability Density Function (PDF) curve.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. Statistical Validation:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t> Output a table comparing the simulated sample mean and variance against the theoretical formulas.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -159,6 +190,25 @@
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -187,13 +237,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -416,7 +469,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="31.6640625" customWidth="1"/>
-    <col min="2" max="2" width="23.33203125" customWidth="1"/>
+    <col min="2" max="2" width="25.5" customWidth="1"/>
     <col min="3" max="3" width="15.1640625" customWidth="1"/>
     <col min="4" max="4" width="18.1640625" customWidth="1"/>
     <col min="5" max="5" width="16.33203125" customWidth="1"/>
@@ -444,33 +497,44 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>4</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="B7" s="7" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="3"/>
+      <c r="B8" s="8"/>
     </row>
     <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="3"/>
+      <c r="B9" s="8"/>
     </row>
     <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="3" t="s">
         <v>6</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
